--- a/hira_material_automation/output/monthly/202601_202604__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__nonmetal_anchor__040019__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-04T21:37:31</t>
+          <t>2026-04-14T21:55:31</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2fa19d3e51580ca3c176d6a291b5737812d5eb8ee42267b96242bf7e229b6924</t>
+          <t>7b18bcaec15f73d902b9f5eeb27a05aaa65d6030d6c30b64b0726b1f485b2b69</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202604__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__nonmetal_anchor__040019__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14T21:55:31</t>
+          <t>2026-04-24T21:53:15</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7b18bcaec15f73d902b9f5eeb27a05aaa65d6030d6c30b64b0726b1f485b2b69</t>
+          <t>e32fc6cb37692c7ad77aed228b09573dd4d73c01d6c5aaaf4734018362ec021f</t>
         </is>
       </c>
     </row>
